--- a/evaluacion_automatica/resultados_metricas_automaticas_base_vs_ft.xlsx
+++ b/evaluacion_automatica/resultados_metricas_automaticas_base_vs_ft.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="247" documentId="11_C406BAF662B6C320AA2BB9DB06FF28CBBF78B702" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E5EFA93-872B-447A-8DEA-50195DAB91DA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E27644FB-0D34-409D-9A9F-F77938B1BB62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
